--- a/artfynd/A 57791-2021 artfynd.xlsx
+++ b/artfynd/A 57791-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57791-2021 artfynd.xlsx
+++ b/artfynd/A 57791-2021 artfynd.xlsx
@@ -675,53 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6909305</v>
+        <v>6909302</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Musmossevägen, södra delen, Lyrestad, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445977.5846305883</v>
+        <v>445978</v>
       </c>
       <c r="R2" t="n">
-        <v>6521108.29154392</v>
+        <v>6521108</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -751,19 +753,14 @@
           <t>2013-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-08-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Under gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +769,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,60 +793,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6909302</v>
+        <v>6909305</v>
       </c>
       <c r="B3" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Musmossevägen, södra delen, Lyrestad, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445977.5846305883</v>
+        <v>445978</v>
       </c>
       <c r="R3" t="n">
-        <v>6521108.29154392</v>
+        <v>6521108</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -878,24 +864,9 @@
           <t>2013-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Under gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57791-2021 artfynd.xlsx
+++ b/artfynd/A 57791-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6909302</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,8 +905,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6909305</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>